--- a/nablarch_sample/アプリケーション方式設計書_1はじめに.xlsx
+++ b/nablarch_sample/アプリケーション方式設計書_1はじめに.xlsx
@@ -1,22 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24326"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9C93A1B-3DA2-434D-B031-3866E3C6F2FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26130"/>
+  <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE2F95B1-CDC5-44D5-989A-C178230EF8C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1245" yWindow="-120" windowWidth="27675" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1.はじめに" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'1.はじめに'!$A$1:$AI$106</definedName>
-    <definedName name="Z_344DE406_F393_4E5A_9A14_596BA958D606_.wvu.PrintArea" localSheetId="0" hidden="1">'1.はじめに'!$A$1:$AI$80</definedName>
-    <definedName name="Z_AC3D26AC_6835_49DE_BCEC_94F40C257790_.wvu.PrintArea" localSheetId="0" hidden="1">'1.はじめに'!$A$1:$AI$80</definedName>
-    <definedName name="Z_B9596DFB_62BC_4685_B6E9_D37718868A8E_.wvu.PrintArea" localSheetId="0" hidden="1">'1.はじめに'!$A$1:$AI$80</definedName>
-    <definedName name="Z_E93A55B4_B092_4477_988B_A2DD8C792DE3_.wvu.PrintArea" localSheetId="0" hidden="1">'1.はじめに'!$A$1:$AI$80</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -33,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="91">
   <si>
     <t>・開発者参照要否</t>
   </si>
@@ -129,14 +122,6 @@
   <si>
     <t xml:space="preserve">
 </t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>（ただし本書は、本書及び上記の別冊と併せて、「Nablarchガイド」「本システム開発標準」「Nablarchサンプルアプリケーション」</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>「NablarchApplicationFramework APIドキュメント」を参照することで、アプリケーション設計・開発作業を実施することが出来るように構成されている。)</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -280,22 +265,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>1.4. 本書におけるJakartaEE仕様への読み替えについて</t>
-    <rPh sb="5" eb="7">
-      <t>ホンショ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="24" eb="25">
-      <t>ヨ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
     <t>特に断りがない限り、以下の表記はJakarta EEの仕様を指すものとする。</t>
     <rPh sb="10" eb="12">
       <t>イカ</t>
@@ -447,6 +416,22 @@
   <si>
     <t>jBatch / JSR352</t>
     <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>本書におけるJakarta EE仕様への読み替えについて</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>（ただし本書は、本書及び上記の別冊と併せて、「Nablarchアプリケーションフレームワーク解説書」「本システム開発標準」</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「NablarchアプリケーションフレームワークExample」「Nablarch APIドキュメント」を参照することで、アプリケーション設計・開発作業を実施する</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ことが出来るように構成されている。)</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -908,13 +893,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
       <xdr:colOff>219808</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>63</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
@@ -932,7 +917,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="828675" y="3543300"/>
+          <a:off x="828675" y="3686175"/>
           <a:ext cx="7954108" cy="5467350"/>
           <a:chOff x="1197" y="5952"/>
           <a:chExt cx="9987" cy="8614"/>
@@ -3512,10 +3497,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AI531"/>
+  <dimension ref="A1:AI532"/>
   <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="16384" width="3.625" style="1"/>
@@ -3529,7 +3514,7 @@
       <c r="C1" s="33"/>
       <c r="D1" s="24"/>
       <c r="E1" s="56" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F1" s="57"/>
       <c r="G1" s="57"/>
@@ -3546,7 +3531,7 @@
       </c>
       <c r="Q1" s="33"/>
       <c r="R1" s="59" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="S1" s="60"/>
       <c r="T1" s="60"/>
@@ -3700,12 +3685,12 @@
     </row>
     <row r="13" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D13" s="35" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D14" s="35" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -3715,12 +3700,12 @@
     </row>
     <row r="16" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D16" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="4:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D17" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="4:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -3730,38 +3715,40 @@
     </row>
     <row r="19" spans="4:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D19" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="4:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D20" s="1" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" spans="4:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D21" s="1" t="s">
-        <v>25</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" spans="4:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D22" s="36" t="s">
+      <c r="D22" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" spans="4:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D23" s="36" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="4:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D23" s="35"/>
-    </row>
     <row r="24" spans="4:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D24" s="34"/>
+      <c r="D24" s="35"/>
     </row>
     <row r="25" spans="4:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D25"/>
+      <c r="D25" s="34"/>
     </row>
     <row r="26" spans="4:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D26" s="34"/>
+      <c r="D26"/>
     </row>
     <row r="27" spans="4:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D27" s="35"/>
+      <c r="D27" s="34"/>
     </row>
     <row r="28" spans="4:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D28" s="35"/>
@@ -3875,161 +3862,129 @@
       <c r="D64" s="35"/>
     </row>
     <row r="65" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C65" s="1" t="str">
+      <c r="D65" s="35"/>
+    </row>
+    <row r="66" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C66" s="1" t="str">
         <f>$B$5&amp;"3."</f>
         <v>1.3.</v>
       </c>
-      <c r="D65" s="1" t="s">
+      <c r="D66" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D66" s="20" t="s">
+    <row r="67" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D67" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E66" s="18"/>
-      <c r="F66" s="18"/>
-      <c r="G66" s="18"/>
-      <c r="H66" s="18"/>
-      <c r="I66" s="18"/>
-      <c r="J66" s="18"/>
-      <c r="K66" s="17"/>
-      <c r="L66" s="19" t="s">
+      <c r="E67" s="18"/>
+      <c r="F67" s="18"/>
+      <c r="G67" s="18"/>
+      <c r="H67" s="18"/>
+      <c r="I67" s="18"/>
+      <c r="J67" s="18"/>
+      <c r="K67" s="17"/>
+      <c r="L67" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="M66" s="18"/>
-      <c r="N66" s="18"/>
-      <c r="O66" s="18"/>
-      <c r="P66" s="17"/>
-      <c r="Q66" s="18" t="s">
+      <c r="M67" s="18"/>
+      <c r="N67" s="18"/>
+      <c r="O67" s="18"/>
+      <c r="P67" s="17"/>
+      <c r="Q67" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="R66" s="18"/>
-      <c r="S66" s="18"/>
-      <c r="T66" s="18"/>
-      <c r="U66" s="18"/>
-      <c r="V66" s="18"/>
-      <c r="W66" s="18"/>
-      <c r="X66" s="18"/>
-      <c r="Y66" s="18"/>
-      <c r="Z66" s="18"/>
-      <c r="AA66" s="18"/>
-      <c r="AB66" s="18"/>
-      <c r="AC66" s="18"/>
-      <c r="AD66" s="18"/>
-      <c r="AE66" s="18"/>
-      <c r="AF66" s="18"/>
-      <c r="AG66" s="18"/>
-      <c r="AH66" s="17"/>
-    </row>
-    <row r="67" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D67" s="16"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="14"/>
-      <c r="I67" s="14"/>
-      <c r="J67" s="14"/>
-      <c r="K67" s="13"/>
-      <c r="L67" s="15" t="s">
+      <c r="R67" s="18"/>
+      <c r="S67" s="18"/>
+      <c r="T67" s="18"/>
+      <c r="U67" s="18"/>
+      <c r="V67" s="18"/>
+      <c r="W67" s="18"/>
+      <c r="X67" s="18"/>
+      <c r="Y67" s="18"/>
+      <c r="Z67" s="18"/>
+      <c r="AA67" s="18"/>
+      <c r="AB67" s="18"/>
+      <c r="AC67" s="18"/>
+      <c r="AD67" s="18"/>
+      <c r="AE67" s="18"/>
+      <c r="AF67" s="18"/>
+      <c r="AG67" s="18"/>
+      <c r="AH67" s="17"/>
+    </row>
+    <row r="68" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D68" s="16"/>
+      <c r="E68" s="14"/>
+      <c r="F68" s="14"/>
+      <c r="G68" s="14"/>
+      <c r="H68" s="14"/>
+      <c r="I68" s="14"/>
+      <c r="J68" s="14"/>
+      <c r="K68" s="13"/>
+      <c r="L68" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="M67" s="14"/>
-      <c r="N67" s="14"/>
-      <c r="O67" s="14"/>
-      <c r="P67" s="13"/>
-      <c r="Q67" s="14"/>
-      <c r="R67" s="14"/>
-      <c r="S67" s="14"/>
-      <c r="T67" s="14"/>
-      <c r="U67" s="14"/>
-      <c r="V67" s="14"/>
-      <c r="W67" s="14"/>
-      <c r="X67" s="14"/>
-      <c r="Y67" s="14"/>
-      <c r="Z67" s="14"/>
-      <c r="AA67" s="14"/>
-      <c r="AB67" s="14"/>
-      <c r="AC67" s="14"/>
-      <c r="AD67" s="14"/>
-      <c r="AE67" s="14"/>
-      <c r="AF67" s="14"/>
-      <c r="AG67" s="14"/>
-      <c r="AH67" s="13"/>
-    </row>
-    <row r="68" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D68" s="12" t="s">
+      <c r="M68" s="14"/>
+      <c r="N68" s="14"/>
+      <c r="O68" s="14"/>
+      <c r="P68" s="13"/>
+      <c r="Q68" s="14"/>
+      <c r="R68" s="14"/>
+      <c r="S68" s="14"/>
+      <c r="T68" s="14"/>
+      <c r="U68" s="14"/>
+      <c r="V68" s="14"/>
+      <c r="W68" s="14"/>
+      <c r="X68" s="14"/>
+      <c r="Y68" s="14"/>
+      <c r="Z68" s="14"/>
+      <c r="AA68" s="14"/>
+      <c r="AB68" s="14"/>
+      <c r="AC68" s="14"/>
+      <c r="AD68" s="14"/>
+      <c r="AE68" s="14"/>
+      <c r="AF68" s="14"/>
+      <c r="AG68" s="14"/>
+      <c r="AH68" s="13"/>
+    </row>
+    <row r="69" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D69" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E69" s="11"/>
+      <c r="F69" s="11"/>
+      <c r="G69" s="11"/>
+      <c r="H69" s="11"/>
+      <c r="I69" s="11"/>
+      <c r="J69" s="11"/>
+      <c r="K69" s="10"/>
+      <c r="L69" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="E68" s="11"/>
-      <c r="F68" s="11"/>
-      <c r="G68" s="11"/>
-      <c r="H68" s="11"/>
-      <c r="I68" s="11"/>
-      <c r="J68" s="11"/>
-      <c r="K68" s="10"/>
-      <c r="L68" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="M68" s="11"/>
-      <c r="N68" s="11"/>
-      <c r="O68" s="11"/>
-      <c r="P68" s="11"/>
-      <c r="Q68" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="R68" s="11"/>
-      <c r="S68" s="11"/>
-      <c r="T68" s="11"/>
-      <c r="U68" s="11"/>
-      <c r="V68" s="11"/>
-      <c r="W68" s="11"/>
-      <c r="X68" s="11"/>
-      <c r="Y68" s="11"/>
-      <c r="Z68" s="11"/>
-      <c r="AA68" s="11"/>
-      <c r="AB68" s="11"/>
-      <c r="AC68" s="11"/>
-      <c r="AD68" s="11"/>
-      <c r="AE68" s="11"/>
-      <c r="AF68" s="11"/>
-      <c r="AG68" s="11"/>
-      <c r="AH68" s="10"/>
-    </row>
-    <row r="69" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D69" s="9"/>
-      <c r="E69" s="4"/>
-      <c r="F69" s="4"/>
-      <c r="G69" s="4"/>
-      <c r="H69" s="4"/>
-      <c r="I69" s="4"/>
-      <c r="J69" s="4"/>
-      <c r="K69" s="8"/>
-      <c r="L69" s="4"/>
-      <c r="M69" s="4"/>
-      <c r="N69" s="4"/>
-      <c r="O69" s="4"/>
-      <c r="P69" s="4"/>
-      <c r="Q69" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="R69" s="4"/>
-      <c r="S69" s="4"/>
-      <c r="T69" s="4"/>
-      <c r="U69" s="4"/>
-      <c r="V69" s="4"/>
-      <c r="W69" s="4"/>
-      <c r="X69" s="4"/>
-      <c r="Y69" s="4"/>
-      <c r="Z69" s="4"/>
-      <c r="AA69" s="4"/>
-      <c r="AB69" s="4"/>
-      <c r="AC69" s="4"/>
-      <c r="AD69" s="4"/>
-      <c r="AE69" s="4"/>
-      <c r="AF69" s="4"/>
-      <c r="AG69" s="4"/>
-      <c r="AH69" s="8"/>
+      <c r="M69" s="11"/>
+      <c r="N69" s="11"/>
+      <c r="O69" s="11"/>
+      <c r="P69" s="11"/>
+      <c r="Q69" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="R69" s="11"/>
+      <c r="S69" s="11"/>
+      <c r="T69" s="11"/>
+      <c r="U69" s="11"/>
+      <c r="V69" s="11"/>
+      <c r="W69" s="11"/>
+      <c r="X69" s="11"/>
+      <c r="Y69" s="11"/>
+      <c r="Z69" s="11"/>
+      <c r="AA69" s="11"/>
+      <c r="AB69" s="11"/>
+      <c r="AC69" s="11"/>
+      <c r="AD69" s="11"/>
+      <c r="AE69" s="11"/>
+      <c r="AF69" s="11"/>
+      <c r="AG69" s="11"/>
+      <c r="AH69" s="10"/>
     </row>
     <row r="70" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D70" s="9"/>
@@ -4046,7 +4001,7 @@
       <c r="O70" s="4"/>
       <c r="P70" s="4"/>
       <c r="Q70" s="9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="R70" s="4"/>
       <c r="S70" s="4"/>
@@ -4081,7 +4036,7 @@
       <c r="O71" s="4"/>
       <c r="P71" s="4"/>
       <c r="Q71" s="9" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="R71" s="4"/>
       <c r="S71" s="4"/>
@@ -4116,7 +4071,7 @@
       <c r="O72" s="4"/>
       <c r="P72" s="4"/>
       <c r="Q72" s="9" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="R72" s="4"/>
       <c r="S72" s="4"/>
@@ -4151,7 +4106,7 @@
       <c r="O73" s="4"/>
       <c r="P73" s="4"/>
       <c r="Q73" s="9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="R73" s="4"/>
       <c r="S73" s="4"/>
@@ -4172,264 +4127,277 @@
       <c r="AH73" s="8"/>
     </row>
     <row r="74" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D74" s="7"/>
-      <c r="E74" s="6"/>
-      <c r="F74" s="6"/>
-      <c r="G74" s="6"/>
-      <c r="H74" s="6"/>
-      <c r="I74" s="6"/>
-      <c r="J74" s="6"/>
-      <c r="K74" s="5"/>
-      <c r="L74" s="6"/>
-      <c r="M74" s="6"/>
-      <c r="N74" s="6"/>
-      <c r="O74" s="6"/>
-      <c r="P74" s="6"/>
-      <c r="Q74" s="7"/>
-      <c r="R74" s="6"/>
-      <c r="S74" s="6"/>
-      <c r="T74" s="6"/>
-      <c r="U74" s="6"/>
-      <c r="V74" s="6"/>
-      <c r="W74" s="6"/>
-      <c r="X74" s="6"/>
-      <c r="Y74" s="6"/>
-      <c r="Z74" s="6"/>
-      <c r="AA74" s="6"/>
-      <c r="AB74" s="6"/>
-      <c r="AC74" s="6"/>
-      <c r="AD74" s="6"/>
-      <c r="AE74" s="6"/>
-      <c r="AF74" s="6"/>
-      <c r="AG74" s="6"/>
-      <c r="AH74" s="5"/>
+      <c r="D74" s="9"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="4"/>
+      <c r="K74" s="8"/>
+      <c r="L74" s="4"/>
+      <c r="M74" s="4"/>
+      <c r="N74" s="4"/>
+      <c r="O74" s="4"/>
+      <c r="P74" s="4"/>
+      <c r="Q74" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="R74" s="4"/>
+      <c r="S74" s="4"/>
+      <c r="T74" s="4"/>
+      <c r="U74" s="4"/>
+      <c r="V74" s="4"/>
+      <c r="W74" s="4"/>
+      <c r="X74" s="4"/>
+      <c r="Y74" s="4"/>
+      <c r="Z74" s="4"/>
+      <c r="AA74" s="4"/>
+      <c r="AB74" s="4"/>
+      <c r="AC74" s="4"/>
+      <c r="AD74" s="4"/>
+      <c r="AE74" s="4"/>
+      <c r="AF74" s="4"/>
+      <c r="AG74" s="4"/>
+      <c r="AH74" s="8"/>
     </row>
     <row r="75" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D75" s="12" t="s">
+      <c r="D75" s="7"/>
+      <c r="E75" s="6"/>
+      <c r="F75" s="6"/>
+      <c r="G75" s="6"/>
+      <c r="H75" s="6"/>
+      <c r="I75" s="6"/>
+      <c r="J75" s="6"/>
+      <c r="K75" s="5"/>
+      <c r="L75" s="6"/>
+      <c r="M75" s="6"/>
+      <c r="N75" s="6"/>
+      <c r="O75" s="6"/>
+      <c r="P75" s="6"/>
+      <c r="Q75" s="7"/>
+      <c r="R75" s="6"/>
+      <c r="S75" s="6"/>
+      <c r="T75" s="6"/>
+      <c r="U75" s="6"/>
+      <c r="V75" s="6"/>
+      <c r="W75" s="6"/>
+      <c r="X75" s="6"/>
+      <c r="Y75" s="6"/>
+      <c r="Z75" s="6"/>
+      <c r="AA75" s="6"/>
+      <c r="AB75" s="6"/>
+      <c r="AC75" s="6"/>
+      <c r="AD75" s="6"/>
+      <c r="AE75" s="6"/>
+      <c r="AF75" s="6"/>
+      <c r="AG75" s="6"/>
+      <c r="AH75" s="5"/>
+    </row>
+    <row r="76" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D76" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E76" s="11"/>
+      <c r="F76" s="11"/>
+      <c r="G76" s="11"/>
+      <c r="H76" s="11"/>
+      <c r="I76" s="11"/>
+      <c r="J76" s="11"/>
+      <c r="K76" s="10"/>
+      <c r="L76" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="M76" s="11"/>
+      <c r="N76" s="11"/>
+      <c r="O76" s="11"/>
+      <c r="P76" s="11"/>
+      <c r="Q76" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="R76" s="11"/>
+      <c r="S76" s="11"/>
+      <c r="T76" s="11"/>
+      <c r="U76" s="11"/>
+      <c r="V76" s="11"/>
+      <c r="W76" s="11"/>
+      <c r="X76" s="11"/>
+      <c r="Y76" s="11"/>
+      <c r="Z76" s="11"/>
+      <c r="AA76" s="11"/>
+      <c r="AB76" s="11"/>
+      <c r="AC76" s="11"/>
+      <c r="AD76" s="11"/>
+      <c r="AE76" s="11"/>
+      <c r="AF76" s="11"/>
+      <c r="AG76" s="11"/>
+      <c r="AH76" s="10"/>
+    </row>
+    <row r="77" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D77" s="9"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+      <c r="G77" s="4"/>
+      <c r="H77" s="4"/>
+      <c r="I77" s="4"/>
+      <c r="J77" s="4"/>
+      <c r="K77" s="8"/>
+      <c r="L77" s="4"/>
+      <c r="M77" s="4"/>
+      <c r="N77" s="4"/>
+      <c r="O77" s="4"/>
+      <c r="P77" s="4"/>
+      <c r="Q77" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="E75" s="11"/>
-      <c r="F75" s="11"/>
-      <c r="G75" s="11"/>
-      <c r="H75" s="11"/>
-      <c r="I75" s="11"/>
-      <c r="J75" s="11"/>
-      <c r="K75" s="10"/>
-      <c r="L75" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="M75" s="11"/>
-      <c r="N75" s="11"/>
-      <c r="O75" s="11"/>
-      <c r="P75" s="11"/>
-      <c r="Q75" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="R75" s="11"/>
-      <c r="S75" s="11"/>
-      <c r="T75" s="11"/>
-      <c r="U75" s="11"/>
-      <c r="V75" s="11"/>
-      <c r="W75" s="11"/>
-      <c r="X75" s="11"/>
-      <c r="Y75" s="11"/>
-      <c r="Z75" s="11"/>
-      <c r="AA75" s="11"/>
-      <c r="AB75" s="11"/>
-      <c r="AC75" s="11"/>
-      <c r="AD75" s="11"/>
-      <c r="AE75" s="11"/>
-      <c r="AF75" s="11"/>
-      <c r="AG75" s="11"/>
-      <c r="AH75" s="10"/>
-    </row>
-    <row r="76" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D76" s="9"/>
-      <c r="E76" s="4"/>
-      <c r="F76" s="4"/>
-      <c r="G76" s="4"/>
-      <c r="H76" s="4"/>
-      <c r="I76" s="4"/>
-      <c r="J76" s="4"/>
-      <c r="K76" s="8"/>
-      <c r="L76" s="4"/>
-      <c r="M76" s="4"/>
-      <c r="N76" s="4"/>
-      <c r="O76" s="4"/>
-      <c r="P76" s="4"/>
-      <c r="Q76" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="R76" s="4"/>
-      <c r="S76" s="4"/>
-      <c r="T76" s="4"/>
-      <c r="U76" s="4"/>
-      <c r="V76" s="4"/>
-      <c r="W76" s="4"/>
-      <c r="X76" s="4"/>
-      <c r="Y76" s="4"/>
-      <c r="Z76" s="4"/>
-      <c r="AA76" s="4"/>
-      <c r="AB76" s="4"/>
-      <c r="AC76" s="4"/>
-      <c r="AD76" s="4"/>
-      <c r="AE76" s="4"/>
-      <c r="AF76" s="4"/>
-      <c r="AG76" s="4"/>
-      <c r="AH76" s="8"/>
-    </row>
-    <row r="77" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D77" s="7"/>
-      <c r="E77" s="6"/>
-      <c r="F77" s="6"/>
-      <c r="G77" s="6"/>
-      <c r="H77" s="6"/>
-      <c r="I77" s="6"/>
-      <c r="J77" s="6"/>
-      <c r="K77" s="5"/>
-      <c r="L77" s="6"/>
-      <c r="M77" s="6"/>
-      <c r="N77" s="6"/>
-      <c r="O77" s="6"/>
-      <c r="P77" s="6"/>
-      <c r="Q77" s="7"/>
-      <c r="R77" s="6"/>
-      <c r="S77" s="6"/>
-      <c r="T77" s="6"/>
-      <c r="U77" s="6"/>
-      <c r="V77" s="6"/>
-      <c r="W77" s="6"/>
-      <c r="X77" s="6"/>
-      <c r="Y77" s="6"/>
-      <c r="Z77" s="6"/>
-      <c r="AA77" s="6"/>
-      <c r="AB77" s="6"/>
-      <c r="AC77" s="6"/>
-      <c r="AD77" s="6"/>
-      <c r="AE77" s="6"/>
-      <c r="AF77" s="6"/>
-      <c r="AG77" s="6"/>
-      <c r="AH77" s="5"/>
+      <c r="R77" s="4"/>
+      <c r="S77" s="4"/>
+      <c r="T77" s="4"/>
+      <c r="U77" s="4"/>
+      <c r="V77" s="4"/>
+      <c r="W77" s="4"/>
+      <c r="X77" s="4"/>
+      <c r="Y77" s="4"/>
+      <c r="Z77" s="4"/>
+      <c r="AA77" s="4"/>
+      <c r="AB77" s="4"/>
+      <c r="AC77" s="4"/>
+      <c r="AD77" s="4"/>
+      <c r="AE77" s="4"/>
+      <c r="AF77" s="4"/>
+      <c r="AG77" s="4"/>
+      <c r="AH77" s="8"/>
     </row>
     <row r="78" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D78" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="E78" s="38"/>
-      <c r="F78" s="38"/>
-      <c r="G78" s="38"/>
-      <c r="H78" s="38"/>
-      <c r="I78" s="38"/>
-      <c r="J78" s="38"/>
-      <c r="K78" s="39"/>
-      <c r="L78" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="M78" s="38"/>
-      <c r="N78" s="38"/>
-      <c r="O78" s="38"/>
-      <c r="P78" s="38"/>
-      <c r="Q78" s="37" t="s">
+      <c r="D78" s="7"/>
+      <c r="E78" s="6"/>
+      <c r="F78" s="6"/>
+      <c r="G78" s="6"/>
+      <c r="H78" s="6"/>
+      <c r="I78" s="6"/>
+      <c r="J78" s="6"/>
+      <c r="K78" s="5"/>
+      <c r="L78" s="6"/>
+      <c r="M78" s="6"/>
+      <c r="N78" s="6"/>
+      <c r="O78" s="6"/>
+      <c r="P78" s="6"/>
+      <c r="Q78" s="7"/>
+      <c r="R78" s="6"/>
+      <c r="S78" s="6"/>
+      <c r="T78" s="6"/>
+      <c r="U78" s="6"/>
+      <c r="V78" s="6"/>
+      <c r="W78" s="6"/>
+      <c r="X78" s="6"/>
+      <c r="Y78" s="6"/>
+      <c r="Z78" s="6"/>
+      <c r="AA78" s="6"/>
+      <c r="AB78" s="6"/>
+      <c r="AC78" s="6"/>
+      <c r="AD78" s="6"/>
+      <c r="AE78" s="6"/>
+      <c r="AF78" s="6"/>
+      <c r="AG78" s="6"/>
+      <c r="AH78" s="5"/>
+    </row>
+    <row r="79" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D79" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="E79" s="38"/>
+      <c r="F79" s="38"/>
+      <c r="G79" s="38"/>
+      <c r="H79" s="38"/>
+      <c r="I79" s="38"/>
+      <c r="J79" s="38"/>
+      <c r="K79" s="39"/>
+      <c r="L79" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="M79" s="38"/>
+      <c r="N79" s="38"/>
+      <c r="O79" s="38"/>
+      <c r="P79" s="38"/>
+      <c r="Q79" s="37" t="s">
+        <v>43</v>
+      </c>
+      <c r="R79" s="38"/>
+      <c r="S79" s="38"/>
+      <c r="T79" s="38"/>
+      <c r="U79" s="38"/>
+      <c r="V79" s="38"/>
+      <c r="W79" s="38"/>
+      <c r="X79" s="38"/>
+      <c r="Y79" s="38"/>
+      <c r="Z79" s="38"/>
+      <c r="AA79" s="38"/>
+      <c r="AB79" s="38"/>
+      <c r="AC79" s="38"/>
+      <c r="AD79" s="38"/>
+      <c r="AE79" s="38"/>
+      <c r="AF79" s="38"/>
+      <c r="AG79" s="38"/>
+      <c r="AH79" s="39"/>
+    </row>
+    <row r="80" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E80" s="3"/>
+    </row>
+    <row r="81" spans="3:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="82" spans="3:21" s="40" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+      <c r="C82" s="1" t="str">
+        <f>$B$5&amp;"4."</f>
+        <v>1.4.</v>
+      </c>
+      <c r="D82" s="40" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="83" spans="3:21" s="40" customFormat="1" ht="11.25" x14ac:dyDescent="0.15"/>
+    <row r="84" spans="3:21" s="40" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+      <c r="D84" s="40" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" s="40" customFormat="1" ht="11.25" x14ac:dyDescent="0.15"/>
+    <row r="86" spans="3:21" s="40" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+      <c r="D86" s="46" t="s">
         <v>45</v>
       </c>
-      <c r="R78" s="38"/>
-      <c r="S78" s="38"/>
-      <c r="T78" s="38"/>
-      <c r="U78" s="38"/>
-      <c r="V78" s="38"/>
-      <c r="W78" s="38"/>
-      <c r="X78" s="38"/>
-      <c r="Y78" s="38"/>
-      <c r="Z78" s="38"/>
-      <c r="AA78" s="38"/>
-      <c r="AB78" s="38"/>
-      <c r="AC78" s="38"/>
-      <c r="AD78" s="38"/>
-      <c r="AE78" s="38"/>
-      <c r="AF78" s="38"/>
-      <c r="AG78" s="38"/>
-      <c r="AH78" s="39"/>
-    </row>
-    <row r="79" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E79" s="3"/>
-    </row>
-    <row r="80" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="81" spans="3:21" s="40" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C81" s="40" t="s">
+      <c r="E86" s="47" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" s="40" customFormat="1" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="83" spans="3:21" s="40" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="D83" s="40" t="s">
+      <c r="F86" s="48"/>
+      <c r="G86" s="48"/>
+      <c r="H86" s="48"/>
+      <c r="I86" s="47" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" s="40" customFormat="1" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="85" spans="3:21" s="40" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="D85" s="46" t="s">
-        <v>48</v>
-      </c>
-      <c r="E85" s="47" t="s">
-        <v>49</v>
-      </c>
-      <c r="F85" s="48"/>
-      <c r="G85" s="48"/>
-      <c r="H85" s="48"/>
-      <c r="I85" s="47" t="s">
-        <v>50</v>
-      </c>
-      <c r="J85" s="49"/>
-      <c r="K85" s="48"/>
-      <c r="L85" s="48"/>
-      <c r="M85" s="48"/>
-      <c r="N85" s="48"/>
-      <c r="O85" s="48"/>
-      <c r="P85" s="48"/>
-      <c r="Q85" s="48"/>
-      <c r="R85" s="48"/>
-      <c r="S85" s="48"/>
-      <c r="T85" s="49"/>
-      <c r="U85" s="41"/>
-    </row>
-    <row r="86" spans="3:21" s="40" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="D86" s="42">
-        <v>1</v>
-      </c>
-      <c r="E86" s="42" t="s">
-        <v>51</v>
-      </c>
-      <c r="F86" s="43"/>
-      <c r="G86" s="43"/>
-      <c r="H86" s="43"/>
-      <c r="I86" s="44" t="s">
-        <v>52</v>
-      </c>
-      <c r="J86" s="45"/>
-      <c r="K86" s="43"/>
-      <c r="L86" s="43"/>
-      <c r="M86" s="43"/>
-      <c r="N86" s="43"/>
-      <c r="O86" s="43"/>
-      <c r="P86" s="43"/>
-      <c r="Q86" s="43"/>
-      <c r="R86" s="43"/>
-      <c r="S86" s="43"/>
-      <c r="T86" s="45"/>
+      <c r="J86" s="49"/>
+      <c r="K86" s="48"/>
+      <c r="L86" s="48"/>
+      <c r="M86" s="48"/>
+      <c r="N86" s="48"/>
+      <c r="O86" s="48"/>
+      <c r="P86" s="48"/>
+      <c r="Q86" s="48"/>
+      <c r="R86" s="48"/>
+      <c r="S86" s="48"/>
+      <c r="T86" s="49"/>
       <c r="U86" s="41"/>
     </row>
     <row r="87" spans="3:21" s="40" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="D87" s="42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E87" s="42" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F87" s="43"/>
       <c r="G87" s="43"/>
       <c r="H87" s="43"/>
       <c r="I87" s="44" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="J87" s="45"/>
       <c r="K87" s="43"/>
@@ -4446,16 +4414,16 @@
     </row>
     <row r="88" spans="3:21" s="40" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="D88" s="42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E88" s="42" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F88" s="43"/>
       <c r="G88" s="43"/>
       <c r="H88" s="43"/>
       <c r="I88" s="44" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="J88" s="45"/>
       <c r="K88" s="43"/>
@@ -4472,16 +4440,16 @@
     </row>
     <row r="89" spans="3:21" s="40" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="D89" s="42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E89" s="42" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F89" s="43"/>
       <c r="G89" s="43"/>
       <c r="H89" s="43"/>
       <c r="I89" s="44" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="J89" s="45"/>
       <c r="K89" s="43"/>
@@ -4498,16 +4466,16 @@
     </row>
     <row r="90" spans="3:21" s="40" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="D90" s="42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E90" s="42" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F90" s="43"/>
       <c r="G90" s="43"/>
       <c r="H90" s="43"/>
       <c r="I90" s="44" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="J90" s="45"/>
       <c r="K90" s="43"/>
@@ -4524,16 +4492,16 @@
     </row>
     <row r="91" spans="3:21" s="40" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="D91" s="42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E91" s="42" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F91" s="43"/>
       <c r="G91" s="43"/>
       <c r="H91" s="43"/>
       <c r="I91" s="44" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="J91" s="45"/>
       <c r="K91" s="43"/>
@@ -4550,16 +4518,16 @@
     </row>
     <row r="92" spans="3:21" s="40" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="D92" s="42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E92" s="42" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="F92" s="43"/>
       <c r="G92" s="43"/>
       <c r="H92" s="43"/>
       <c r="I92" s="44" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="J92" s="45"/>
       <c r="K92" s="43"/>
@@ -4576,16 +4544,16 @@
     </row>
     <row r="93" spans="3:21" s="40" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="D93" s="42">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E93" s="42" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="F93" s="43"/>
       <c r="G93" s="43"/>
       <c r="H93" s="43"/>
       <c r="I93" s="44" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="J93" s="45"/>
       <c r="K93" s="43"/>
@@ -4602,16 +4570,16 @@
     </row>
     <row r="94" spans="3:21" s="40" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="D94" s="42">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E94" s="42" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F94" s="43"/>
       <c r="G94" s="43"/>
       <c r="H94" s="43"/>
       <c r="I94" s="44" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="J94" s="45"/>
       <c r="K94" s="43"/>
@@ -4628,16 +4596,16 @@
     </row>
     <row r="95" spans="3:21" s="40" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="D95" s="42">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E95" s="42" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="F95" s="43"/>
       <c r="G95" s="43"/>
       <c r="H95" s="43"/>
       <c r="I95" s="44" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="J95" s="45"/>
       <c r="K95" s="43"/>
@@ -4654,16 +4622,16 @@
     </row>
     <row r="96" spans="3:21" s="40" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="D96" s="42">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E96" s="42" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F96" s="43"/>
       <c r="G96" s="43"/>
       <c r="H96" s="43"/>
       <c r="I96" s="44" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="J96" s="45"/>
       <c r="K96" s="43"/>
@@ -4680,16 +4648,16 @@
     </row>
     <row r="97" spans="4:34" s="40" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="D97" s="42">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E97" s="42" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F97" s="43"/>
       <c r="G97" s="43"/>
       <c r="H97" s="43"/>
       <c r="I97" s="44" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="J97" s="45"/>
       <c r="K97" s="43"/>
@@ -4706,16 +4674,16 @@
     </row>
     <row r="98" spans="4:34" s="40" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="D98" s="42">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E98" s="42" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F98" s="43"/>
       <c r="G98" s="43"/>
       <c r="H98" s="43"/>
       <c r="I98" s="44" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="J98" s="45"/>
       <c r="K98" s="43"/>
@@ -4732,16 +4700,16 @@
     </row>
     <row r="99" spans="4:34" s="40" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="D99" s="42">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E99" s="42" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F99" s="43"/>
       <c r="G99" s="43"/>
       <c r="H99" s="43"/>
       <c r="I99" s="44" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="J99" s="45"/>
       <c r="K99" s="43"/>
@@ -4758,16 +4726,16 @@
     </row>
     <row r="100" spans="4:34" s="40" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="D100" s="42">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E100" s="42" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F100" s="43"/>
       <c r="G100" s="43"/>
       <c r="H100" s="43"/>
       <c r="I100" s="44" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="J100" s="45"/>
       <c r="K100" s="43"/>
@@ -4784,16 +4752,16 @@
     </row>
     <row r="101" spans="4:34" s="40" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="D101" s="42">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E101" s="42" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F101" s="43"/>
       <c r="G101" s="43"/>
       <c r="H101" s="43"/>
       <c r="I101" s="44" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="J101" s="45"/>
       <c r="K101" s="43"/>
@@ -4810,16 +4778,16 @@
     </row>
     <row r="102" spans="4:34" s="40" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="D102" s="42">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E102" s="42" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F102" s="43"/>
       <c r="G102" s="43"/>
       <c r="H102" s="43"/>
       <c r="I102" s="44" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="J102" s="45"/>
       <c r="K102" s="43"/>
@@ -4836,16 +4804,16 @@
     </row>
     <row r="103" spans="4:34" s="40" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="D103" s="42">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E103" s="42" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F103" s="43"/>
       <c r="G103" s="43"/>
       <c r="H103" s="43"/>
       <c r="I103" s="44" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="J103" s="45"/>
       <c r="K103" s="43"/>
@@ -4862,16 +4830,16 @@
     </row>
     <row r="104" spans="4:34" s="40" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="D104" s="42">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E104" s="42" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F104" s="43"/>
       <c r="G104" s="43"/>
       <c r="H104" s="43"/>
       <c r="I104" s="44" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J104" s="45"/>
       <c r="K104" s="43"/>
@@ -4886,59 +4854,84 @@
       <c r="T104" s="45"/>
       <c r="U104" s="41"/>
     </row>
-    <row r="105" spans="4:34" s="40" customFormat="1" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="106" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F106" s="4"/>
-      <c r="G106" s="4"/>
-      <c r="H106" s="4"/>
-      <c r="I106" s="4"/>
-      <c r="J106" s="4"/>
-      <c r="K106" s="4"/>
-      <c r="L106" s="4"/>
-      <c r="M106" s="4"/>
-      <c r="N106" s="4"/>
-      <c r="O106" s="4"/>
-      <c r="P106" s="4"/>
-      <c r="Q106" s="4"/>
-      <c r="R106" s="4"/>
-      <c r="S106" s="4"/>
-      <c r="T106" s="4"/>
-      <c r="U106" s="4"/>
-      <c r="V106" s="4"/>
-      <c r="W106" s="4"/>
-      <c r="X106" s="4"/>
-      <c r="Y106" s="4"/>
-      <c r="Z106" s="4"/>
-      <c r="AA106" s="4"/>
-      <c r="AB106" s="4"/>
-      <c r="AC106" s="4"/>
-      <c r="AD106" s="4"/>
-      <c r="AE106" s="4"/>
-      <c r="AF106" s="4"/>
-      <c r="AG106" s="4"/>
-      <c r="AH106" s="4"/>
-    </row>
+    <row r="105" spans="4:34" s="40" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+      <c r="D105" s="42">
+        <v>19</v>
+      </c>
+      <c r="E105" s="42" t="s">
+        <v>83</v>
+      </c>
+      <c r="F105" s="43"/>
+      <c r="G105" s="43"/>
+      <c r="H105" s="43"/>
+      <c r="I105" s="44" t="s">
+        <v>84</v>
+      </c>
+      <c r="J105" s="45"/>
+      <c r="K105" s="43"/>
+      <c r="L105" s="43"/>
+      <c r="M105" s="43"/>
+      <c r="N105" s="43"/>
+      <c r="O105" s="43"/>
+      <c r="P105" s="43"/>
+      <c r="Q105" s="43"/>
+      <c r="R105" s="43"/>
+      <c r="S105" s="43"/>
+      <c r="T105" s="45"/>
+      <c r="U105" s="41"/>
+    </row>
+    <row r="106" spans="4:34" s="40" customFormat="1" ht="11.25" x14ac:dyDescent="0.15"/>
     <row r="107" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E107" s="3"/>
+      <c r="F107" s="4"/>
+      <c r="G107" s="4"/>
+      <c r="H107" s="4"/>
+      <c r="I107" s="4"/>
+      <c r="J107" s="4"/>
+      <c r="K107" s="4"/>
+      <c r="L107" s="4"/>
+      <c r="M107" s="4"/>
+      <c r="N107" s="4"/>
+      <c r="O107" s="4"/>
+      <c r="P107" s="4"/>
+      <c r="Q107" s="4"/>
+      <c r="R107" s="4"/>
+      <c r="S107" s="4"/>
+      <c r="T107" s="4"/>
+      <c r="U107" s="4"/>
+      <c r="V107" s="4"/>
+      <c r="W107" s="4"/>
+      <c r="X107" s="4"/>
+      <c r="Y107" s="4"/>
+      <c r="Z107" s="4"/>
+      <c r="AA107" s="4"/>
+      <c r="AB107" s="4"/>
+      <c r="AC107" s="4"/>
+      <c r="AD107" s="4"/>
+      <c r="AE107" s="4"/>
+      <c r="AF107" s="4"/>
+      <c r="AG107" s="4"/>
+      <c r="AH107" s="4"/>
     </row>
     <row r="108" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F108" s="2"/>
-    </row>
-    <row r="109" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="110" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E110" s="3"/>
-    </row>
+      <c r="E108" s="3"/>
+    </row>
+    <row r="109" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F109" s="2"/>
+    </row>
+    <row r="110" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="111" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F111" s="2"/>
-    </row>
-    <row r="112" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="113" spans="5:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E113" s="3"/>
-    </row>
+      <c r="E111" s="3"/>
+    </row>
+    <row r="112" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F112" s="2"/>
+    </row>
+    <row r="113" spans="5:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="114" spans="5:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F114" s="2"/>
-    </row>
-    <row r="115" spans="5:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+      <c r="E114" s="3"/>
+    </row>
+    <row r="115" spans="5:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F115" s="2"/>
+    </row>
     <row r="116" spans="5:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="117" spans="5:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="118" spans="5:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -5355,6 +5348,7 @@
     <row r="529" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="530" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="531" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="532" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="AA3:AE3"/>
@@ -5371,31 +5365,31 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <hyperlinks>
-    <hyperlink ref="AB86" r:id="rId1" display="https://jakarta.ee/specifications/faces/" xr:uid="{782B74A1-89FC-480C-AE47-7C2520095F9A}"/>
-    <hyperlink ref="AB87" r:id="rId2" display="https://jakarta.ee/specifications/authentication/" xr:uid="{6C06BB29-4933-4C88-B41A-B0AAA657D3A9}"/>
-    <hyperlink ref="AB88" r:id="rId3" display="https://jakarta.ee/specifications/authorization/" xr:uid="{BBB03EDE-15E8-4005-AED7-30E923F89391}"/>
-    <hyperlink ref="AB89" r:id="rId4" display="https://jakarta.ee/specifications/messaging/" xr:uid="{72C31096-8AC7-4347-8582-2CC62C44DC73}"/>
-    <hyperlink ref="AB90" r:id="rId5" display="https://jakarta.ee/specifications/persistence/" xr:uid="{3DBDD60C-3BBC-45EB-82D1-D853F873E999}"/>
-    <hyperlink ref="AB91" r:id="rId6" display="https://jakarta.ee/specifications/transactions/" xr:uid="{5D688F39-A34D-4C5A-858D-B3EA812C6354}"/>
-    <hyperlink ref="AB92" r:id="rId7" display="https://jakarta.ee/specifications/batch/" xr:uid="{BA519FE1-39F7-4575-8800-D4ECA62A4672}"/>
-    <hyperlink ref="AB93" r:id="rId8" display="https://jakarta.ee/specifications/connectors/" xr:uid="{1DDCC83F-DC00-4CCD-8673-A7E27FB9D8FE}"/>
-    <hyperlink ref="AB94" r:id="rId9" display="https://jakarta.ee/specifications/activation/" xr:uid="{A82BF3B3-D769-4C05-9EED-4055CA13CABA}"/>
-    <hyperlink ref="AB95" r:id="rId10" display="https://jakarta.ee/specifications/expression-language/" xr:uid="{21619010-89F8-4EA9-8831-6EC957CC1F48}"/>
-    <hyperlink ref="AB96" r:id="rId11" display="https://jakarta.ee/specifications/enterprise-beans/" xr:uid="{C5F54307-D617-4471-B421-E09C264A1B99}"/>
-    <hyperlink ref="AB97" r:id="rId12" display="https://jakarta.ee/specifications/xml-binding/" xr:uid="{4C14C032-4474-4EEC-A103-5C4C274D58E6}"/>
-    <hyperlink ref="AB98" r:id="rId13" display="https://jakarta.ee/specifications/jsonb/" xr:uid="{02B4DFEB-C762-4AD0-B13E-33ECBDD78F12}"/>
-    <hyperlink ref="AB99" r:id="rId14" display="https://jakarta.ee/specifications/jsonp/" xr:uid="{131DFA28-7FA9-4EDA-B88F-D5CEE6B1EC48}"/>
-    <hyperlink ref="AB100" r:id="rId15" display="https://jakarta.ee/specifications/pages/" xr:uid="{112828A6-064D-4355-B811-4434E4708436}"/>
-    <hyperlink ref="AB101" r:id="rId16" display="https://jakarta.ee/specifications/xml-web-services/" xr:uid="{A439A1CD-1FD5-4481-BF7C-734038061FBF}"/>
-    <hyperlink ref="AB102" r:id="rId17" display="https://jakarta.ee/specifications/restful-ws/" xr:uid="{361F1A55-B566-4540-8D9B-977071236FC0}"/>
-    <hyperlink ref="AB103" r:id="rId18" display="https://jakarta.ee/specifications/tags/" xr:uid="{EE417ADE-AD06-4BDF-A2C1-DB97994F2816}"/>
-    <hyperlink ref="AB104" r:id="rId19" display="https://jakarta.ee/specifications/cdi/" xr:uid="{79E3E807-CF9C-4C0B-8EB3-F6D1AB359447}"/>
+    <hyperlink ref="AB87" r:id="rId1" display="https://jakarta.ee/specifications/faces/" xr:uid="{782B74A1-89FC-480C-AE47-7C2520095F9A}"/>
+    <hyperlink ref="AB88" r:id="rId2" display="https://jakarta.ee/specifications/authentication/" xr:uid="{6C06BB29-4933-4C88-B41A-B0AAA657D3A9}"/>
+    <hyperlink ref="AB89" r:id="rId3" display="https://jakarta.ee/specifications/authorization/" xr:uid="{BBB03EDE-15E8-4005-AED7-30E923F89391}"/>
+    <hyperlink ref="AB90" r:id="rId4" display="https://jakarta.ee/specifications/messaging/" xr:uid="{72C31096-8AC7-4347-8582-2CC62C44DC73}"/>
+    <hyperlink ref="AB91" r:id="rId5" display="https://jakarta.ee/specifications/persistence/" xr:uid="{3DBDD60C-3BBC-45EB-82D1-D853F873E999}"/>
+    <hyperlink ref="AB92" r:id="rId6" display="https://jakarta.ee/specifications/transactions/" xr:uid="{5D688F39-A34D-4C5A-858D-B3EA812C6354}"/>
+    <hyperlink ref="AB93" r:id="rId7" display="https://jakarta.ee/specifications/batch/" xr:uid="{BA519FE1-39F7-4575-8800-D4ECA62A4672}"/>
+    <hyperlink ref="AB94" r:id="rId8" display="https://jakarta.ee/specifications/connectors/" xr:uid="{1DDCC83F-DC00-4CCD-8673-A7E27FB9D8FE}"/>
+    <hyperlink ref="AB95" r:id="rId9" display="https://jakarta.ee/specifications/activation/" xr:uid="{A82BF3B3-D769-4C05-9EED-4055CA13CABA}"/>
+    <hyperlink ref="AB96" r:id="rId10" display="https://jakarta.ee/specifications/expression-language/" xr:uid="{21619010-89F8-4EA9-8831-6EC957CC1F48}"/>
+    <hyperlink ref="AB97" r:id="rId11" display="https://jakarta.ee/specifications/enterprise-beans/" xr:uid="{C5F54307-D617-4471-B421-E09C264A1B99}"/>
+    <hyperlink ref="AB98" r:id="rId12" display="https://jakarta.ee/specifications/xml-binding/" xr:uid="{4C14C032-4474-4EEC-A103-5C4C274D58E6}"/>
+    <hyperlink ref="AB99" r:id="rId13" display="https://jakarta.ee/specifications/jsonb/" xr:uid="{02B4DFEB-C762-4AD0-B13E-33ECBDD78F12}"/>
+    <hyperlink ref="AB100" r:id="rId14" display="https://jakarta.ee/specifications/jsonp/" xr:uid="{131DFA28-7FA9-4EDA-B88F-D5CEE6B1EC48}"/>
+    <hyperlink ref="AB101" r:id="rId15" display="https://jakarta.ee/specifications/pages/" xr:uid="{112828A6-064D-4355-B811-4434E4708436}"/>
+    <hyperlink ref="AB102" r:id="rId16" display="https://jakarta.ee/specifications/xml-web-services/" xr:uid="{A439A1CD-1FD5-4481-BF7C-734038061FBF}"/>
+    <hyperlink ref="AB103" r:id="rId17" display="https://jakarta.ee/specifications/restful-ws/" xr:uid="{361F1A55-B566-4540-8D9B-977071236FC0}"/>
+    <hyperlink ref="AB104" r:id="rId18" display="https://jakarta.ee/specifications/tags/" xr:uid="{EE417ADE-AD06-4BDF-A2C1-DB97994F2816}"/>
+    <hyperlink ref="AB105" r:id="rId19" display="https://jakarta.ee/specifications/cdi/" xr:uid="{79E3E807-CF9C-4C0B-8EB3-F6D1AB359447}"/>
   </hyperlinks>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId20"/>
   <rowBreaks count="2" manualBreakCount="2">
-    <brk id="22" max="34" man="1"/>
-    <brk id="64" max="34" man="1"/>
+    <brk id="23" max="34" man="1"/>
+    <brk id="65" max="34" man="1"/>
   </rowBreaks>
   <drawing r:id="rId21"/>
 </worksheet>
